--- a/src/main/resources/templates/USER_PROFILE.xlsx
+++ b/src/main/resources/templates/USER_PROFILE.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面\SpringBootWorkSpace\customized-validation-demo\src\main\resources\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面\ModuleWorkSpace\customized-validation-module\src\main\resources\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1C4EDC2-9312-4D30-B54F-850A76382220}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63EAFD9A-A959-4B66-9CA3-A0BDF2F4B667}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{4A3D1D62-1966-42DA-B660-403B4A06D9C6}"/>
   </bookViews>
   <sheets>
-    <sheet name="USER" sheetId="1" r:id="rId1"/>
-    <sheet name="DEPT" sheetId="2" r:id="rId2"/>
+    <sheet name="使用者名單" sheetId="1" r:id="rId1"/>
+    <sheet name="所屬部門" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -26,41 +26,45 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
   <si>
     <t>C123456789</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>AGE</t>
+    <t>s</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技術開發處</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>姓名</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>SEX</t>
+    <t>年齡</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>NATION_ID</t>
+    <t>性別</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>DEPT</t>
+    <t>身分證字號</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>員工編號</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>JOB_TITLE</t>
+    <t>職稱</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>EMP_NO</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NAME</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>s</t>
+    <t>部門</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -441,16 +445,16 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -462,7 +466,7 @@
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -481,7 +485,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63CBABCE-610F-4A22-9A4F-AEE15F69C36B}">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="9.44140625" bestFit="1" customWidth="1"/>
@@ -490,16 +494,21 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" t="s">
         <v>7</v>
       </c>
-      <c r="B1" t="s">
-        <v>6</v>
-      </c>
       <c r="C1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D1" t="s">
-        <v>4</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
